--- a/data/raw_data/20251002_scholarid.xlsx
+++ b/data/raw_data/20251002_scholarid.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://radbouduniversiteit-my.sharepoint.com/personal/jos_slabbekoorn_ru_nl/Documents/project - network/data/raw_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4835" documentId="8_{9FC1B398-DD7A-4026-9B5C-236889A5F066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40F8D18A-2CDD-414E-A94B-D650E6B7B380}"/>
+  <xr:revisionPtr revIDLastSave="5274" documentId="8_{9FC1B398-DD7A-4026-9B5C-236889A5F066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23D86AF7-1FCE-A04A-AAAA-DBA91A02E5DC}"/>
   <bookViews>
-    <workbookView xWindow="-7840" yWindow="-21100" windowWidth="38400" windowHeight="19720" activeTab="3" xr2:uid="{3A988D9E-DED3-CC44-BA34-7C0A3852FE51}"/>
+    <workbookView xWindow="-7860" yWindow="-28180" windowWidth="25620" windowHeight="28180" activeTab="1" xr2:uid="{3A988D9E-DED3-CC44-BA34-7C0A3852FE51}"/>
   </bookViews>
   <sheets>
     <sheet name="Sociologie_old" sheetId="1" r:id="rId1"/>
@@ -353,7 +353,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7859" uniqueCount="3230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8157" uniqueCount="3311">
   <si>
     <t xml:space="preserve">Naam </t>
   </si>
@@ -10044,13 +10044,256 @@
   </si>
   <si>
     <t>e.j.p.zwarthoed@vu.nl</t>
+  </si>
+  <si>
+    <t>Jacob Alabab-Moser</t>
+  </si>
+  <si>
+    <t>Adria Albareda Sanz</t>
+  </si>
+  <si>
+    <t>alabab-moser@essb.eur.nl</t>
+  </si>
+  <si>
+    <t>albaredasanz@essb.eur.nl</t>
+  </si>
+  <si>
+    <t>Marjolijn Antheunis</t>
+  </si>
+  <si>
+    <t>Full Professor</t>
+  </si>
+  <si>
+    <t>antheunis@essb.eur.nl</t>
+  </si>
+  <si>
+    <t>Ids Baalbergen</t>
+  </si>
+  <si>
+    <t>baalbergen@essb.eur.nl</t>
+  </si>
+  <si>
+    <t>PostDoc</t>
+  </si>
+  <si>
+    <t>Joris Beek</t>
+  </si>
+  <si>
+    <t>Victor Bekkers</t>
+  </si>
+  <si>
+    <t>Thijs van den Berg</t>
+  </si>
+  <si>
+    <t>Robin Bouwman</t>
+  </si>
+  <si>
+    <t>Romit Chowdhury</t>
+  </si>
+  <si>
+    <t>Dragos Ciulinaru</t>
+  </si>
+  <si>
+    <t>Laura Cleton</t>
+  </si>
+  <si>
+    <t>Marjolijn Das</t>
+  </si>
+  <si>
+    <t>Geske Dijkstra</t>
+  </si>
+  <si>
+    <t>Wolfgan Ebbers</t>
+  </si>
+  <si>
+    <t>Clara Egger</t>
+  </si>
+  <si>
+    <t>Jiska Engelbert</t>
+  </si>
+  <si>
+    <t>Han Entzinger</t>
+  </si>
+  <si>
+    <t>Menno Fenger</t>
+  </si>
+  <si>
+    <t>Paola Fezzigna</t>
+  </si>
+  <si>
+    <t>Tineke Fokkema</t>
+  </si>
+  <si>
+    <t>Manou Gomlich</t>
+  </si>
+  <si>
+    <t>Francisca Gromme</t>
+  </si>
+  <si>
+    <t>Markus Haverland</t>
+  </si>
+  <si>
+    <t>Vincent Homburg</t>
+  </si>
+  <si>
+    <t>Maaike Hornstra</t>
+  </si>
+  <si>
+    <t>Glenn Houtgraaf</t>
+  </si>
+  <si>
+    <t>Alex Huang</t>
+  </si>
+  <si>
+    <t>Rins Hylkema</t>
+  </si>
+  <si>
+    <t>Gabriele Jacobs</t>
+  </si>
+  <si>
+    <t>Arthur de Jaeger</t>
+  </si>
+  <si>
+    <t>Petra de Jong</t>
+  </si>
+  <si>
+    <t>Maarten de Jong</t>
+  </si>
+  <si>
+    <t>Elina Jonitz</t>
+  </si>
+  <si>
+    <t>Philip Karre</t>
+  </si>
+  <si>
+    <t>Hannah Kay</t>
+  </si>
+  <si>
+    <t>Krista King</t>
+  </si>
+  <si>
+    <t>Manon Koopman</t>
+  </si>
+  <si>
+    <t>Katharina Krusselmann</t>
+  </si>
+  <si>
+    <t>Phuong Hoan Le</t>
+  </si>
+  <si>
+    <t>Thijs Lidner</t>
+  </si>
+  <si>
+    <t>Derk Loorbach</t>
+  </si>
+  <si>
+    <t>Gabriele Marie</t>
+  </si>
+  <si>
+    <t>Peter Mascini</t>
+  </si>
+  <si>
+    <t>Miriam Matthiessen</t>
+  </si>
+  <si>
+    <t>Shreyas Meher</t>
+  </si>
+  <si>
+    <t>Koen Migchelbrink</t>
+  </si>
+  <si>
+    <t>Manaar Mohammed</t>
+  </si>
+  <si>
+    <t>David Moloney</t>
+  </si>
+  <si>
+    <t>Malin Nemeth</t>
+  </si>
+  <si>
+    <t>Wybren Nooitgedagt</t>
+  </si>
+  <si>
+    <t>Michal Onderco</t>
+  </si>
+  <si>
+    <t>Tom Oreel</t>
+  </si>
+  <si>
+    <t>Ina Paredis</t>
+  </si>
+  <si>
+    <t>Kees van Paridon</t>
+  </si>
+  <si>
+    <t>Asya Pisarevskaya</t>
+  </si>
+  <si>
+    <t>Julia Reinold</t>
+  </si>
+  <si>
+    <t>Meghan Rens</t>
+  </si>
+  <si>
+    <t>Jan Rotmans</t>
+  </si>
+  <si>
+    <t>Maria Schiller</t>
+  </si>
+  <si>
+    <t>Peter Scholten</t>
+  </si>
+  <si>
+    <t>Jorgen Schram</t>
+  </si>
+  <si>
+    <t>Stefano Scibilia</t>
+  </si>
+  <si>
+    <t>Dimitrii Shchetinin</t>
+  </si>
+  <si>
+    <t>Loise Smink</t>
+  </si>
+  <si>
+    <t>Martijn van der Steen</t>
+  </si>
+  <si>
+    <t>Bram Steijn</t>
+  </si>
+  <si>
+    <t>Sandra van Thiel</t>
+  </si>
+  <si>
+    <t>Andrey Tibajev</t>
+  </si>
+  <si>
+    <t>Pieter Tuytens</t>
+  </si>
+  <si>
+    <t>Marcus van Twist</t>
+  </si>
+  <si>
+    <t>Carola Vasileiadi</t>
+  </si>
+  <si>
+    <t>Brenda Vermeeren</t>
+  </si>
+  <si>
+    <t>Lenone Verweij</t>
+  </si>
+  <si>
+    <t>Rianne Warsen</t>
+  </si>
+  <si>
+    <t>Asya Zhelyazkova</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -10081,12 +10324,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -10115,7 +10352,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -10132,7 +10369,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -19198,7 +19434,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EA0E808-A69A-D240-B9DA-35830F5E25A7}">
-  <dimension ref="A1:F393"/>
+  <dimension ref="A1:F491"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
@@ -24611,6 +24847,1096 @@
       </c>
       <c r="D393" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A394" t="s">
+        <v>3230</v>
+      </c>
+      <c r="B394" t="s">
+        <v>6</v>
+      </c>
+      <c r="C394" t="s">
+        <v>3232</v>
+      </c>
+      <c r="D394" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A395" t="s">
+        <v>3231</v>
+      </c>
+      <c r="B395" t="s">
+        <v>6</v>
+      </c>
+      <c r="C395" t="s">
+        <v>3233</v>
+      </c>
+      <c r="D395" t="s">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A396" t="s">
+        <v>3234</v>
+      </c>
+      <c r="B396" t="s">
+        <v>6</v>
+      </c>
+      <c r="C396" t="s">
+        <v>3236</v>
+      </c>
+      <c r="D396" t="s">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A397" t="s">
+        <v>3237</v>
+      </c>
+      <c r="B397" t="s">
+        <v>6</v>
+      </c>
+      <c r="C397" t="s">
+        <v>3238</v>
+      </c>
+      <c r="D397" t="s">
+        <v>3239</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A398" t="s">
+        <v>3240</v>
+      </c>
+      <c r="B398" t="s">
+        <v>6</v>
+      </c>
+      <c r="D398" t="s">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A399" t="s">
+        <v>3241</v>
+      </c>
+      <c r="B399" t="s">
+        <v>6</v>
+      </c>
+      <c r="D399" t="s">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A400" t="s">
+        <v>3242</v>
+      </c>
+      <c r="B400" t="s">
+        <v>6</v>
+      </c>
+      <c r="D400" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A401" t="s">
+        <v>3243</v>
+      </c>
+      <c r="B401" t="s">
+        <v>6</v>
+      </c>
+      <c r="D401" t="s">
+        <v>3097</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A402" t="s">
+        <v>116</v>
+      </c>
+      <c r="B402" t="s">
+        <v>6</v>
+      </c>
+      <c r="D402" t="s">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A403" t="s">
+        <v>3244</v>
+      </c>
+      <c r="B403" t="s">
+        <v>6</v>
+      </c>
+      <c r="D403" t="s">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A404" t="s">
+        <v>3245</v>
+      </c>
+      <c r="B404" t="s">
+        <v>6</v>
+      </c>
+      <c r="D404" t="s">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A405" t="s">
+        <v>3246</v>
+      </c>
+      <c r="B405" t="s">
+        <v>6</v>
+      </c>
+      <c r="D405" t="s">
+        <v>3239</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A406" t="s">
+        <v>60</v>
+      </c>
+      <c r="B406" t="s">
+        <v>6</v>
+      </c>
+      <c r="D406" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A407" t="s">
+        <v>130</v>
+      </c>
+      <c r="B407" t="s">
+        <v>6</v>
+      </c>
+      <c r="D407" t="s">
+        <v>3239</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A408" t="s">
+        <v>3247</v>
+      </c>
+      <c r="B408" t="s">
+        <v>6</v>
+      </c>
+      <c r="D408" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A409" t="s">
+        <v>3248</v>
+      </c>
+      <c r="B409" t="s">
+        <v>6</v>
+      </c>
+      <c r="D409" t="s">
+        <v>3049</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A410" t="s">
+        <v>87</v>
+      </c>
+      <c r="B410" t="s">
+        <v>6</v>
+      </c>
+      <c r="D410" t="s">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A411" t="s">
+        <v>121</v>
+      </c>
+      <c r="B411" t="s">
+        <v>6</v>
+      </c>
+      <c r="D411" t="s">
+        <v>3049</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A412" t="s">
+        <v>3249</v>
+      </c>
+      <c r="B412" t="s">
+        <v>6</v>
+      </c>
+      <c r="D412" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A413" t="s">
+        <v>3250</v>
+      </c>
+      <c r="B413" t="s">
+        <v>6</v>
+      </c>
+      <c r="D413" t="s">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A414" t="s">
+        <v>158</v>
+      </c>
+      <c r="B414" t="s">
+        <v>6</v>
+      </c>
+      <c r="D414" t="s">
+        <v>3097</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A415" t="s">
+        <v>52</v>
+      </c>
+      <c r="B415" t="s">
+        <v>6</v>
+      </c>
+      <c r="D415" t="s">
+        <v>3049</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A416" t="s">
+        <v>3251</v>
+      </c>
+      <c r="B416" t="s">
+        <v>6</v>
+      </c>
+      <c r="D416" t="s">
+        <v>3097</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A417" t="s">
+        <v>55</v>
+      </c>
+      <c r="B417" t="s">
+        <v>6</v>
+      </c>
+      <c r="D417" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A418" t="s">
+        <v>3252</v>
+      </c>
+      <c r="B418" t="s">
+        <v>6</v>
+      </c>
+      <c r="D418" t="s">
+        <v>3049</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A419" t="s">
+        <v>3253</v>
+      </c>
+      <c r="B419" t="s">
+        <v>6</v>
+      </c>
+      <c r="D419" t="s">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A420" t="s">
+        <v>3254</v>
+      </c>
+      <c r="B420" t="s">
+        <v>6</v>
+      </c>
+      <c r="D420" t="s">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A421" t="s">
+        <v>3255</v>
+      </c>
+      <c r="B421" t="s">
+        <v>6</v>
+      </c>
+      <c r="D421" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A422" t="s">
+        <v>24</v>
+      </c>
+      <c r="B422" t="s">
+        <v>6</v>
+      </c>
+      <c r="D422" t="s">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A423" t="s">
+        <v>3256</v>
+      </c>
+      <c r="B423" t="s">
+        <v>6</v>
+      </c>
+      <c r="D423" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A424" t="s">
+        <v>72</v>
+      </c>
+      <c r="B424" t="s">
+        <v>6</v>
+      </c>
+      <c r="D424" t="s">
+        <v>3097</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A425" t="s">
+        <v>3257</v>
+      </c>
+      <c r="B425" t="s">
+        <v>6</v>
+      </c>
+      <c r="D425" t="s">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A426" t="s">
+        <v>44</v>
+      </c>
+      <c r="B426" t="s">
+        <v>6</v>
+      </c>
+      <c r="D426" t="s">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A427" t="s">
+        <v>3258</v>
+      </c>
+      <c r="B427" t="s">
+        <v>6</v>
+      </c>
+      <c r="D427" t="s">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A428" t="s">
+        <v>30</v>
+      </c>
+      <c r="B428" t="s">
+        <v>6</v>
+      </c>
+      <c r="D428" t="s">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A429" t="s">
+        <v>2527</v>
+      </c>
+      <c r="B429" t="s">
+        <v>6</v>
+      </c>
+      <c r="D429" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A430" t="s">
+        <v>3259</v>
+      </c>
+      <c r="B430" t="s">
+        <v>6</v>
+      </c>
+      <c r="D430" t="s">
+        <v>3097</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A431" t="s">
+        <v>3260</v>
+      </c>
+      <c r="B431" t="s">
+        <v>6</v>
+      </c>
+      <c r="D431" t="s">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A432" t="s">
+        <v>3261</v>
+      </c>
+      <c r="B432" t="s">
+        <v>6</v>
+      </c>
+      <c r="D432" t="s">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A433" t="s">
+        <v>3262</v>
+      </c>
+      <c r="B433" t="s">
+        <v>6</v>
+      </c>
+      <c r="D433" t="s">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A434" t="s">
+        <v>3263</v>
+      </c>
+      <c r="B434" t="s">
+        <v>6</v>
+      </c>
+      <c r="D434" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A435" t="s">
+        <v>3264</v>
+      </c>
+      <c r="B435" t="s">
+        <v>6</v>
+      </c>
+      <c r="D435" t="s">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A436" t="s">
+        <v>3265</v>
+      </c>
+      <c r="B436" t="s">
+        <v>6</v>
+      </c>
+      <c r="D436" t="s">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A437" t="s">
+        <v>3266</v>
+      </c>
+      <c r="B437" t="s">
+        <v>6</v>
+      </c>
+      <c r="D437" t="s">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A438" t="s">
+        <v>3267</v>
+      </c>
+      <c r="B438" t="s">
+        <v>6</v>
+      </c>
+      <c r="D438" t="s">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A439" t="s">
+        <v>3268</v>
+      </c>
+      <c r="B439" t="s">
+        <v>6</v>
+      </c>
+      <c r="D439" t="s">
+        <v>2995</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A440" t="s">
+        <v>5</v>
+      </c>
+      <c r="B440" t="s">
+        <v>6</v>
+      </c>
+      <c r="D440" t="s">
+        <v>3097</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A441" t="s">
+        <v>3269</v>
+      </c>
+      <c r="B441" t="s">
+        <v>6</v>
+      </c>
+      <c r="D441" t="s">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A442" t="s">
+        <v>3270</v>
+      </c>
+      <c r="B442" t="s">
+        <v>6</v>
+      </c>
+      <c r="D442" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A443" t="s">
+        <v>124</v>
+      </c>
+      <c r="B443" t="s">
+        <v>6</v>
+      </c>
+      <c r="D443" t="s">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A444" t="s">
+        <v>3271</v>
+      </c>
+      <c r="B444" t="s">
+        <v>6</v>
+      </c>
+      <c r="D444" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A445" t="s">
+        <v>3272</v>
+      </c>
+      <c r="B445" t="s">
+        <v>6</v>
+      </c>
+      <c r="D445" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A446" t="s">
+        <v>40</v>
+      </c>
+      <c r="B446" t="s">
+        <v>6</v>
+      </c>
+      <c r="D446" t="s">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A447" t="s">
+        <v>3273</v>
+      </c>
+      <c r="B447" t="s">
+        <v>6</v>
+      </c>
+      <c r="D447" t="s">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A448" t="s">
+        <v>3274</v>
+      </c>
+      <c r="B448" t="s">
+        <v>6</v>
+      </c>
+      <c r="D448" t="s">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A449" t="s">
+        <v>21</v>
+      </c>
+      <c r="B449" t="s">
+        <v>6</v>
+      </c>
+      <c r="D449" t="s">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A450" t="s">
+        <v>3275</v>
+      </c>
+      <c r="B450" t="s">
+        <v>6</v>
+      </c>
+      <c r="D450" t="s">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A451" t="s">
+        <v>3276</v>
+      </c>
+      <c r="B451" t="s">
+        <v>6</v>
+      </c>
+      <c r="D451" t="s">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A452" t="s">
+        <v>3277</v>
+      </c>
+      <c r="B452" t="s">
+        <v>6</v>
+      </c>
+      <c r="D452" t="s">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A453" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B453" t="s">
+        <v>6</v>
+      </c>
+      <c r="D453" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A454" t="s">
+        <v>3278</v>
+      </c>
+      <c r="B454" t="s">
+        <v>6</v>
+      </c>
+      <c r="D454" t="s">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A455" t="s">
+        <v>3279</v>
+      </c>
+      <c r="B455" t="s">
+        <v>6</v>
+      </c>
+      <c r="D455" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A456" t="s">
+        <v>3280</v>
+      </c>
+      <c r="B456" t="s">
+        <v>6</v>
+      </c>
+      <c r="D456" t="s">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A457" t="s">
+        <v>133</v>
+      </c>
+      <c r="B457" t="s">
+        <v>6</v>
+      </c>
+      <c r="D457" t="s">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A458" t="s">
+        <v>136</v>
+      </c>
+      <c r="B458" t="s">
+        <v>6</v>
+      </c>
+      <c r="D458" t="s">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A459" t="s">
+        <v>3281</v>
+      </c>
+      <c r="B459" t="s">
+        <v>6</v>
+      </c>
+      <c r="D459" t="s">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A460" t="s">
+        <v>3282</v>
+      </c>
+      <c r="B460" t="s">
+        <v>6</v>
+      </c>
+      <c r="D460" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A461" t="s">
+        <v>3283</v>
+      </c>
+      <c r="B461" t="s">
+        <v>6</v>
+      </c>
+      <c r="D461" t="s">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A462" t="s">
+        <v>3284</v>
+      </c>
+      <c r="B462" t="s">
+        <v>6</v>
+      </c>
+      <c r="D462" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A463" t="s">
+        <v>3285</v>
+      </c>
+      <c r="B463" t="s">
+        <v>6</v>
+      </c>
+      <c r="D463" t="s">
+        <v>3239</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A464" t="s">
+        <v>3286</v>
+      </c>
+      <c r="B464" t="s">
+        <v>6</v>
+      </c>
+      <c r="D464" t="s">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A465" t="s">
+        <v>3287</v>
+      </c>
+      <c r="B465" t="s">
+        <v>6</v>
+      </c>
+      <c r="D465" t="s">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A466" t="s">
+        <v>113</v>
+      </c>
+      <c r="B466" t="s">
+        <v>6</v>
+      </c>
+      <c r="D466" t="s">
+        <v>3097</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A467" t="s">
+        <v>3288</v>
+      </c>
+      <c r="B467" t="s">
+        <v>6</v>
+      </c>
+      <c r="D467" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A468" t="s">
+        <v>3289</v>
+      </c>
+      <c r="B468" t="s">
+        <v>6</v>
+      </c>
+      <c r="D468" t="s">
+        <v>3049</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A469" t="s">
+        <v>3290</v>
+      </c>
+      <c r="B469" t="s">
+        <v>6</v>
+      </c>
+      <c r="D469" t="s">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A470" t="s">
+        <v>3291</v>
+      </c>
+      <c r="B470" t="s">
+        <v>6</v>
+      </c>
+      <c r="D470" t="s">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A471" t="s">
+        <v>3292</v>
+      </c>
+      <c r="B471" t="s">
+        <v>6</v>
+      </c>
+      <c r="D471" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A472" t="s">
+        <v>3293</v>
+      </c>
+      <c r="B472" t="s">
+        <v>6</v>
+      </c>
+      <c r="D472" t="s">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A473" t="s">
+        <v>3294</v>
+      </c>
+      <c r="B473" t="s">
+        <v>6</v>
+      </c>
+      <c r="D473" t="s">
+        <v>3097</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A474" t="s">
+        <v>3295</v>
+      </c>
+      <c r="B474" t="s">
+        <v>6</v>
+      </c>
+      <c r="D474" t="s">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A475" t="s">
+        <v>3296</v>
+      </c>
+      <c r="B475" t="s">
+        <v>6</v>
+      </c>
+      <c r="D475" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A476" t="s">
+        <v>3297</v>
+      </c>
+      <c r="B476" t="s">
+        <v>6</v>
+      </c>
+      <c r="D476" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A477" t="s">
+        <v>3298</v>
+      </c>
+      <c r="B477" t="s">
+        <v>6</v>
+      </c>
+      <c r="D477" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A478" t="s">
+        <v>3299</v>
+      </c>
+      <c r="B478" t="s">
+        <v>6</v>
+      </c>
+      <c r="D478" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A479" t="s">
+        <v>3300</v>
+      </c>
+      <c r="B479" t="s">
+        <v>6</v>
+      </c>
+      <c r="D479" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A480" t="s">
+        <v>3301</v>
+      </c>
+      <c r="B480" t="s">
+        <v>6</v>
+      </c>
+      <c r="D480" t="s">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A481" t="s">
+        <v>152</v>
+      </c>
+      <c r="B481" t="s">
+        <v>6</v>
+      </c>
+      <c r="D481" t="s">
+        <v>3097</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A482" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B482" t="s">
+        <v>6</v>
+      </c>
+      <c r="D482" t="s">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A483" t="s">
+        <v>3303</v>
+      </c>
+      <c r="B483" t="s">
+        <v>6</v>
+      </c>
+      <c r="D483" t="s">
+        <v>3184</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A484" t="s">
+        <v>14</v>
+      </c>
+      <c r="B484" t="s">
+        <v>6</v>
+      </c>
+      <c r="D484" t="s">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A485" t="s">
+        <v>3304</v>
+      </c>
+      <c r="B485" t="s">
+        <v>6</v>
+      </c>
+      <c r="D485" t="s">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A486" t="s">
+        <v>3305</v>
+      </c>
+      <c r="B486" t="s">
+        <v>6</v>
+      </c>
+      <c r="D486" t="s">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A487" t="s">
+        <v>3306</v>
+      </c>
+      <c r="B487" t="s">
+        <v>6</v>
+      </c>
+      <c r="D487" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A488" t="s">
+        <v>3307</v>
+      </c>
+      <c r="B488" t="s">
+        <v>6</v>
+      </c>
+      <c r="D488" t="s">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A489" t="s">
+        <v>3308</v>
+      </c>
+      <c r="B489" t="s">
+        <v>6</v>
+      </c>
+      <c r="D489" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A490" t="s">
+        <v>3309</v>
+      </c>
+      <c r="B490" t="s">
+        <v>6</v>
+      </c>
+      <c r="D490" t="s">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A491" t="s">
+        <v>3310</v>
+      </c>
+      <c r="B491" t="s">
+        <v>6</v>
+      </c>
+      <c r="D491" t="s">
+        <v>3097</v>
       </c>
     </row>
   </sheetData>
@@ -36851,7 +38177,7 @@
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A285" s="10" t="s">
+      <c r="A285" t="s">
         <v>2295</v>
       </c>
       <c r="B285" t="s">
@@ -37266,7 +38592,7 @@
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A308" s="10" t="s">
+      <c r="A308" t="s">
         <v>2314</v>
       </c>
       <c r="B308" t="s">
